--- a/files/jinyu_award_2021.xlsx
+++ b/files/jinyu_award_2021.xlsx
@@ -49,10 +49,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>songlingyi@Email.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>指导老师</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -170,6 +166,10 @@
   </si>
   <si>
     <t>莫行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lynne@Email.com</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -270,7 +270,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -286,14 +286,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -568,7 +571,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -602,7 +605,7 @@
         <v>6</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -613,110 +616,110 @@
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>7</v>
+      <c r="E2" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="C5" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
+      <c r="A6" s="9"/>
       <c r="B6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
+      <c r="A7" s="9"/>
       <c r="B7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
